--- a/data/trans_dic/P15A-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P15A-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,86; 9,52</t>
+          <t>4,73; 9,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,83</t>
+          <t>3,04; 7,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 6,3</t>
+          <t>2,32; 6,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,48</t>
+          <t>0,51; 5,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,92</t>
+          <t>1,22; 3,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,66</t>
+          <t>0,99; 3,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,98</t>
+          <t>0,49; 2,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 6,8</t>
+          <t>0,78; 7,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,17</t>
+          <t>3,4; 6,17</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,79</t>
+          <t>2,33; 4,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,04</t>
+          <t>1,77; 4,16</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,91</t>
+          <t>1,04; 4,86</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,6</t>
+          <t>3,27; 6,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 6,91</t>
+          <t>3,33; 7,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,58</t>
+          <t>2,39; 5,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,6</t>
+          <t>1,4; 5,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,68</t>
+          <t>1,73; 4,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,76</t>
+          <t>1,06; 3,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,95</t>
+          <t>0,8; 3,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,29</t>
+          <t>0,35; 2,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,07</t>
+          <t>2,94; 5,17</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,72</t>
+          <t>2,56; 4,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,77</t>
+          <t>1,9; 3,83</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,3</t>
+          <t>0,96; 3,19</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,63</t>
+          <t>1,31; 3,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,86</t>
+          <t>1,26; 3,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,64</t>
+          <t>1,72; 4,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,48</t>
+          <t>0,91; 3,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,26</t>
+          <t>1,11; 3,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,83</t>
+          <t>0,81; 2,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,16</t>
+          <t>0,87; 3,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,85</t>
+          <t>1,0; 2,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,04</t>
+          <t>1,53; 3,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,83</t>
+          <t>1,3; 2,87</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,38</t>
+          <t>1,57; 3,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,74</t>
+          <t>1,16; 2,72</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,67</t>
+          <t>2,24; 5,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,53</t>
+          <t>0,65; 2,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,28</t>
+          <t>1,0; 3,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,93</t>
+          <t>0,88; 4,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,4</t>
+          <t>0,97; 3,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 5,02</t>
+          <t>1,89; 4,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,81</t>
+          <t>0,76; 2,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,59</t>
+          <t>0,97; 2,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,05</t>
+          <t>1,88; 4,06</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,22</t>
+          <t>1,4; 3,19</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,68</t>
+          <t>1,1; 2,72</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,93</t>
+          <t>1,17; 2,94</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,67</t>
+          <t>1,18; 4,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,55</t>
+          <t>0,25; 2,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,93</t>
+          <t>0,22; 2,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,07</t>
+          <t>0,53; 2,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,39</t>
+          <t>1,22; 4,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,19</t>
+          <t>1,69; 5,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,94</t>
+          <t>1,47; 4,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,57</t>
+          <t>1,53; 3,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,69</t>
+          <t>1,53; 3,91</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,15</t>
+          <t>1,24; 3,22</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,94</t>
+          <t>1,19; 3,09</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,46</t>
+          <t>1,13; 2,46</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,37</t>
+          <t>0,6; 3,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,78</t>
+          <t>1,27; 4,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,01</t>
+          <t>0,55; 3,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,42</t>
+          <t>0,87; 2,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,99</t>
+          <t>1,36; 4,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,94; 5,94</t>
+          <t>1,98; 5,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,54; 7,0</t>
+          <t>2,37; 6,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,64</t>
+          <t>1,12; 4,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,53</t>
+          <t>1,26; 3,43</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,67</t>
+          <t>2,08; 4,87</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,6</t>
+          <t>1,89; 4,64</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,37</t>
+          <t>1,15; 3,49</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 6,08</t>
+          <t>1,12; 5,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,32</t>
+          <t>1,66; 6,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 5,66</t>
+          <t>1,58; 5,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,0</t>
+          <t>1,87; 4,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,35; 10,18</t>
+          <t>4,14; 9,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,91; 7,48</t>
+          <t>2,98; 7,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,13; 8,3</t>
+          <t>3,35; 8,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,81; 8,27</t>
+          <t>4,77; 8,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,55; 7,28</t>
+          <t>3,49; 7,63</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,91; 6,19</t>
+          <t>2,81; 6,12</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,99; 6,51</t>
+          <t>3,02; 6,69</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,01; 6,3</t>
+          <t>3,98; 6,34</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,12; 4,42</t>
+          <t>3,15; 4,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,34; 3,56</t>
+          <t>2,34; 3,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,19</t>
+          <t>2,09; 3,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,82</t>
+          <t>1,52; 2,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,4</t>
+          <t>2,23; 3,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,38</t>
+          <t>2,21; 3,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,11</t>
+          <t>1,95; 3,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,13</t>
+          <t>1,96; 3,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,85; 3,77</t>
+          <t>2,87; 3,75</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,39; 3,24</t>
+          <t>2,43; 3,27</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,17; 2,97</t>
+          <t>2,2; 2,97</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,89; 2,71</t>
+          <t>1,88; 2,69</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23991; 47058</t>
+          <t>23362; 47032</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13612; 31027</t>
+          <t>13790; 31941</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10055; 26440</t>
+          <t>9735; 26962</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1867; 21929</t>
+          <t>2034; 23767</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5707; 18309</t>
+          <t>5702; 18289</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4117; 15740</t>
+          <t>4250; 16705</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1959; 11778</t>
+          <t>1950; 11411</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2547; 21286</t>
+          <t>2438; 22228</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33219; 59375</t>
+          <t>32697; 59306</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20196; 42320</t>
+          <t>20590; 41231</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14291; 32901</t>
+          <t>14413; 33876</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6377; 34990</t>
+          <t>7428; 34686</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24905; 48566</t>
+          <t>24058; 49195</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23384; 47479</t>
+          <t>22891; 48848</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14395; 32963</t>
+          <t>14099; 33313</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5587; 23704</t>
+          <t>5939; 23755</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10731; 29295</t>
+          <t>10796; 29337</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6136; 22952</t>
+          <t>6443; 22447</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4412; 16606</t>
+          <t>4529; 17435</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1758; 11736</t>
+          <t>1771; 12706</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39993; 68961</t>
+          <t>40031; 70330</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33312; 61279</t>
+          <t>33160; 61632</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21638; 43545</t>
+          <t>21929; 44251</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8762; 30858</t>
+          <t>8935; 29814</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8617; 23200</t>
+          <t>8397; 24849</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9025; 26305</t>
+          <t>8611; 27098</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12030; 31016</t>
+          <t>11513; 30842</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4992; 18676</t>
+          <t>4858; 18948</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7686; 22457</t>
+          <t>7627; 22268</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6537; 20085</t>
+          <t>5745; 19979</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5451; 20894</t>
+          <t>5765; 21497</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5210; 15465</t>
+          <t>5448; 15425</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18477; 40424</t>
+          <t>20289; 43602</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17783; 39440</t>
+          <t>18134; 39916</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21767; 44987</t>
+          <t>20853; 43948</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12304; 29576</t>
+          <t>12527; 29393</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12270; 29441</t>
+          <t>11628; 29923</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3962; 15537</t>
+          <t>3989; 15376</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6167; 21178</t>
+          <t>6482; 21403</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8150; 34863</t>
+          <t>7854; 36232</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4315; 17520</t>
+          <t>5014; 18307</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11836; 30946</t>
+          <t>11676; 30536</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4813; 18207</t>
+          <t>4909; 18258</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7087; 18429</t>
+          <t>6882; 18214</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20163; 41959</t>
+          <t>19403; 42011</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18696; 39586</t>
+          <t>17249; 39260</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14152; 34654</t>
+          <t>14280; 35289</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18462; 46968</t>
+          <t>18721; 47034</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4634; 18050</t>
+          <t>4572; 17783</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1112; 10965</t>
+          <t>1081; 10396</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1030; 9227</t>
+          <t>1036; 10428</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3077; 11595</t>
+          <t>2965; 12212</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4963; 17730</t>
+          <t>4940; 17419</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7547; 23244</t>
+          <t>7552; 22722</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7605; 24567</t>
+          <t>7322; 23958</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8382; 19573</t>
+          <t>8361; 18958</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11848; 29174</t>
+          <t>12115; 30941</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10708; 27611</t>
+          <t>10884; 28289</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11080; 28639</t>
+          <t>11620; 30148</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13159; 27253</t>
+          <t>12540; 27286</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1688; 9874</t>
+          <t>1761; 10074</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3921; 14800</t>
+          <t>3923; 14347</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1844; 10067</t>
+          <t>1835; 10420</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3372; 12608</t>
+          <t>3219; 11016</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5233; 17108</t>
+          <t>4665; 16587</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6882; 21036</t>
+          <t>7019; 19913</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9606; 26428</t>
+          <t>8937; 25353</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6784; 28242</t>
+          <t>6823; 28595</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7445; 22460</t>
+          <t>8030; 21805</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13585; 31028</t>
+          <t>13783; 32298</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12996; 32744</t>
+          <t>13458; 33032</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11721; 32910</t>
+          <t>11202; 34050</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2599; 12755</t>
+          <t>2359; 12075</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3965; 15801</t>
+          <t>4136; 16530</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4002; 14558</t>
+          <t>4056; 14453</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5148; 14150</t>
+          <t>5294; 13760</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>14536; 33998</t>
+          <t>13833; 32433</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11305; 29107</t>
+          <t>11577; 30444</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12508; 33208</t>
+          <t>13401; 32927</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>20476; 35223</t>
+          <t>20302; 35015</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>19320; 39577</t>
+          <t>18993; 41511</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18577; 39570</t>
+          <t>17920; 39089</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19658; 42775</t>
+          <t>19859; 43959</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>28406; 44670</t>
+          <t>28198; 44894</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>102111; 144855</t>
+          <t>103130; 147090</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>80016; 122151</t>
+          <t>80175; 120595</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>72684; 108185</t>
+          <t>71065; 108483</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>54522; 97424</t>
+          <t>52714; 97446</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>75288; 115059</t>
+          <t>75267; 116065</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>79889; 120306</t>
+          <t>78736; 119152</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>71030; 110136</t>
+          <t>69056; 107560</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>73012; 114774</t>
+          <t>71915; 111038</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>189848; 251213</t>
+          <t>190759; 249424</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>167014; 226559</t>
+          <t>169870; 228695</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>150790; 205997</t>
+          <t>152738; 206076</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>134783; 193208</t>
+          <t>133759; 191295</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15A-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P15A-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,73; 9,52</t>
+          <t>4,83; 9,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 7,03</t>
+          <t>2,88; 6,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 6,43</t>
+          <t>2,55; 6,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,94</t>
+          <t>0,37; 6,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,91</t>
+          <t>1,15; 3,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,88</t>
+          <t>0,9; 3,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,88</t>
+          <t>0,49; 2,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 7,1</t>
+          <t>0,63; 6,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,4; 6,17</t>
+          <t>3,34; 6,03</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,66</t>
+          <t>2,35; 4,91</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,16</t>
+          <t>1,66; 4,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,86</t>
+          <t>1,04; 4,94</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,27; 6,69</t>
+          <t>3,36; 6,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,33; 7,11</t>
+          <t>3,42; 7,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,64</t>
+          <t>2,47; 5,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 5,61</t>
+          <t>1,51; 6,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,69</t>
+          <t>1,75; 4,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,68</t>
+          <t>1,0; 3,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,09</t>
+          <t>0,79; 3,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,48</t>
+          <t>0,36; 2,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,17</t>
+          <t>2,84; 5,07</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,75</t>
+          <t>2,53; 4,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,83</t>
+          <t>1,92; 3,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,19</t>
+          <t>1,26; 3,56</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -997,52 +997,52 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,89</t>
+          <t>1,24; 3,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,97</t>
+          <t>1,27; 3,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,61</t>
+          <t>1,87; 4,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,53</t>
+          <t>1,01; 3,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,23</t>
+          <t>1,01; 3,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,81</t>
+          <t>0,83; 2,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,25</t>
+          <t>0,89; 3,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,84</t>
+          <t>0,94; 2,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,28</t>
+          <t>1,38; 2,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,87</t>
+          <t>1,24; 2,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,72</t>
+          <t>1,2; 2,69</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 5,76</t>
+          <t>2,28; 5,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,5</t>
+          <t>0,65; 2,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,31</t>
+          <t>0,99; 3,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,08</t>
+          <t>1,99; 4,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,55</t>
+          <t>0,97; 3,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,96</t>
+          <t>1,86; 4,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,81</t>
+          <t>0,76; 2,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,55</t>
+          <t>1,09; 2,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,06</t>
+          <t>1,88; 4,1</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,19</t>
+          <t>1,5; 3,21</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,72</t>
+          <t>1,05; 2,61</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,94</t>
+          <t>1,76; 3,4</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,6</t>
+          <t>1,22; 4,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,42</t>
+          <t>0,25; 2,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,18</t>
+          <t>0,22; 2,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,18</t>
+          <t>0,61; 2,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,31</t>
+          <t>1,2; 4,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,07</t>
+          <t>1,64; 5,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,82</t>
+          <t>1,46; 4,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,46</t>
+          <t>1,47; 3,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,91</t>
+          <t>1,53; 3,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,22</t>
+          <t>1,23; 3,18</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,09</t>
+          <t>1,17; 2,93</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,46</t>
+          <t>1,21; 2,47</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,44</t>
+          <t>0,61; 3,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,63</t>
+          <t>1,27; 4,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,12</t>
+          <t>0,53; 3,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,99</t>
+          <t>0,89; 3,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,84</t>
+          <t>1,3; 4,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,98; 5,63</t>
+          <t>2,14; 5,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,37; 6,71</t>
+          <t>2,53; 6,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,7</t>
+          <t>3,08; 5,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,43</t>
+          <t>1,18; 3,43</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,87</t>
+          <t>1,96; 4,66</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,64</t>
+          <t>1,78; 4,41</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,49</t>
+          <t>2,26; 3,99</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 5,75</t>
+          <t>1,2; 6,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,66; 6,62</t>
+          <t>1,63; 6,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,62</t>
+          <t>1,58; 5,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,87</t>
+          <t>1,74; 5,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,14; 9,71</t>
+          <t>4,36; 10,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,98; 7,83</t>
+          <t>2,95; 7,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,35; 8,23</t>
+          <t>3,18; 8,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,77; 8,22</t>
+          <t>4,76; 8,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,49; 7,63</t>
+          <t>3,6; 7,67</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,81; 6,12</t>
+          <t>2,81; 6,26</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,02; 6,69</t>
+          <t>3,0; 6,64</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,98; 6,34</t>
+          <t>3,95; 6,22</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,27 +1664,27 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
           <t>2,5%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,15; 4,49</t>
+          <t>3,14; 4,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,34; 3,52</t>
+          <t>2,3; 3,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,2</t>
+          <t>2,09; 3,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,82</t>
+          <t>1,84; 3,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,43</t>
+          <t>2,25; 3,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,21; 3,35</t>
+          <t>2,26; 3,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,03</t>
+          <t>1,97; 3,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,03</t>
+          <t>2,22; 3,2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,87; 3,75</t>
+          <t>2,86; 3,72</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,43; 3,27</t>
+          <t>2,41; 3,25</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,2; 2,97</t>
+          <t>2,2; 2,96</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,88; 2,69</t>
+          <t>2,15; 2,92</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7814</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8826</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16640</t>
+          <t>17618</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23362; 47032</t>
+          <t>23885; 46850</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13790; 31941</t>
+          <t>13099; 30683</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9735; 26962</t>
+          <t>10690; 26890</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2034; 23767</t>
+          <t>1496; 25750</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5702; 18289</t>
+          <t>5381; 18433</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4250; 16705</t>
+          <t>3893; 15708</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1950; 11411</t>
+          <t>1938; 11229</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2438; 22228</t>
+          <t>2295; 23406</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32697; 59306</t>
+          <t>32156; 57984</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20590; 41231</t>
+          <t>20791; 43379</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14413; 33876</t>
+          <t>13560; 33706</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7428; 34686</t>
+          <t>7988; 38031</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11758</t>
+          <t>15735</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5049</t>
+          <t>5065</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16808</t>
+          <t>20799</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24058; 49195</t>
+          <t>24706; 47626</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22891; 48848</t>
+          <t>23472; 48565</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14099; 33313</t>
+          <t>14610; 32378</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5939; 23755</t>
+          <t>7182; 28709</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10796; 29337</t>
+          <t>10973; 29012</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6443; 22447</t>
+          <t>6121; 22664</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4529; 17435</t>
+          <t>4464; 17448</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1771; 12706</t>
+          <t>1821; 11227</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40031; 70330</t>
+          <t>38674; 69050</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33160; 61632</t>
+          <t>32760; 62916</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21929; 44251</t>
+          <t>22168; 43156</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8935; 29814</t>
+          <t>12309; 34858</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10172</t>
+          <t>11859</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19491</t>
+          <t>22180</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8397; 24849</t>
+          <t>7914; 23976</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8611; 27098</t>
+          <t>8670; 26155</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11513; 30842</t>
+          <t>12484; 31283</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4858; 18948</t>
+          <t>6248; 22310</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7627; 22268</t>
+          <t>6966; 22118</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5745; 19979</t>
+          <t>5933; 20181</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5765; 21497</t>
+          <t>5857; 20480</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5448; 15425</t>
+          <t>5820; 16162</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20289; 43602</t>
+          <t>18322; 39570</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18134; 39916</t>
+          <t>17284; 40641</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20853; 43948</t>
+          <t>20910; 43867</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12527; 29393</t>
+          <t>14908; 33445</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21618</t>
+          <t>22526</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11668</t>
+          <t>12832</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>33286</t>
+          <t>35358</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11628; 29923</t>
+          <t>11822; 30135</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3989; 15376</t>
+          <t>4002; 15967</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6482; 21403</t>
+          <t>6423; 22414</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7854; 36232</t>
+          <t>13921; 34658</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5014; 18307</t>
+          <t>4989; 18861</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11676; 30536</t>
+          <t>11484; 30640</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4909; 18258</t>
+          <t>4919; 19008</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6882; 18214</t>
+          <t>8005; 19804</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19403; 42011</t>
+          <t>19463; 42456</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17249; 39260</t>
+          <t>18509; 39506</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14280; 35289</t>
+          <t>13588; 33775</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18721; 47034</t>
+          <t>25366; 48941</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6603</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12916</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19518</t>
+          <t>21630</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4572; 17783</t>
+          <t>4723; 18567</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1081; 10396</t>
+          <t>1088; 10357</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1036; 10428</t>
+          <t>1038; 10107</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2965; 12212</t>
+          <t>3729; 14153</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4940; 17419</t>
+          <t>4836; 17757</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7552; 22722</t>
+          <t>7358; 22814</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7322; 23958</t>
+          <t>7270; 24319</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8361; 18958</t>
+          <t>8975; 20138</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12115; 30941</t>
+          <t>12112; 30017</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10884; 28289</t>
+          <t>10808; 27937</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11620; 30148</t>
+          <t>11383; 28575</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12540; 27286</t>
+          <t>14738; 30127</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>16762</t>
+          <t>18759</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>23138</t>
+          <t>25761</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1761; 10074</t>
+          <t>1773; 10325</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3923; 14347</t>
+          <t>3941; 15034</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1835; 10420</t>
+          <t>1757; 10356</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3219; 11016</t>
+          <t>3635; 12546</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4665; 16587</t>
+          <t>4463; 16494</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7019; 19913</t>
+          <t>7564; 20678</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8937; 25353</t>
+          <t>9543; 25468</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6823; 28595</t>
+          <t>13520; 25755</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8030; 21805</t>
+          <t>7526; 21811</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13783; 32298</t>
+          <t>12989; 30907</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13458; 33032</t>
+          <t>12674; 31408</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11202; 34050</t>
+          <t>19087; 33741</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8589</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>26946</t>
+          <t>28734</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>35535</t>
+          <t>38435</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2359; 12075</t>
+          <t>2521; 12831</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4136; 16530</t>
+          <t>4084; 15921</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4056; 14453</t>
+          <t>4066; 14044</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5294; 13760</t>
+          <t>5400; 15824</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>13833; 32433</t>
+          <t>14555; 34539</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11577; 30444</t>
+          <t>11486; 29427</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13401; 32927</t>
+          <t>12738; 32128</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>20302; 35015</t>
+          <t>22103; 37248</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>18993; 41511</t>
+          <t>19578; 41710</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17920; 39089</t>
+          <t>17926; 40014</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19859; 43959</t>
+          <t>19709; 43649</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>28198; 44894</t>
+          <t>30609; 48221</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>72930</t>
+          <t>82343</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>91486</t>
+          <t>99438</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>164416</t>
+          <t>181781</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>103130; 147090</t>
+          <t>102848; 146963</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>80175; 120595</t>
+          <t>78985; 119930</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>71065; 108483</t>
+          <t>70895; 108804</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>52714; 97446</t>
+          <t>65126; 107011</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>75267; 116065</t>
+          <t>75895; 113942</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>78736; 119152</t>
+          <t>80274; 120256</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>69056; 107560</t>
+          <t>69712; 110150</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>71915; 111038</t>
+          <t>82827; 119612</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>190759; 249424</t>
+          <t>190398; 247827</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>169870; 228695</t>
+          <t>168303; 227313</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>152738; 206076</t>
+          <t>152632; 205724</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>133759; 191295</t>
+          <t>156515; 211970</t>
         </is>
       </c>
     </row>
